--- a/metadata/Plate3/SRKW_Diet_Plate3_MetaData.xlsx
+++ b/metadata/Plate3/SRKW_Diet_Plate3_MetaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lfallon/Library/Application Support/Box/Box Edit/Documents/2071235497602/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9EF70B-8C61-2546-80DB-6AAAAB6C8513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF574CC0-F9A5-F74F-8E13-6FFE170E72C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7940" yWindow="620" windowWidth="16700" windowHeight="22820" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
+    <workbookView xWindow="28080" yWindow="600" windowWidth="16700" windowHeight="22820" xr2:uid="{518B7A33-C5FE-E642-B8D5-47A99A98280E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="126">
   <si>
     <t>Sample_name</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>MOCK3</t>
+  </si>
+  <si>
+    <t>K26</t>
   </si>
 </sst>
 </file>
@@ -466,17 +469,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,6 +964,9 @@
       <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
@@ -1180,6 +1185,9 @@
       <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="C18" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
@@ -1703,7 +1711,7 @@
       <c r="B41" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" t="s">
         <v>113</v>
       </c>
       <c r="D41" t="s">
@@ -1726,7 +1734,7 @@
       <c r="B42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" t="s">
         <v>114</v>
       </c>
       <c r="D42" t="s">
@@ -1791,6 +1799,9 @@
       </c>
       <c r="B45" s="2" t="s">
         <v>60</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="D45" t="s">
         <v>8</v>
